--- a/results/link-prediction-gcn/Link/5shot/Wisconsin/GCN_total_results.xlsx
+++ b/results/link-prediction-gcn/Link/5shot/Wisconsin/GCN_total_results.xlsx
@@ -893,457 +893,457 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.4375±0.0000</t>
+          <t>0.4931±0.0098</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.5208±0.0000</t>
+          <t>0.5417±0.0295</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.5208±0.0000</t>
+          <t>0.5486±0.0354</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>0.5000±0.0295</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.5556±0.0491</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.6875±0.0000</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0.5764±0.0428</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.5486±0.0428</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.5486±0.0428</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>0.6250±0.0000</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>0.5417±0.0000</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0.4583±0.0000</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>0.5694±0.0354</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0.5694±0.0354</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0.5833±0.0680</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0.5208±0.0450</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>0.5764±0.0428</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>0.5486±0.0196</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0.5625±0.0900</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0.5625±0.0900</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0.5625±0.0900</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0.5764±0.0354</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0.5833±0.0613</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>0.6111±0.0354</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>0.6319±0.0967</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>0.5417±0.0589</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>0.4931±0.0260</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>0.4861±0.0260</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0.5139±0.0196</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0.5347±0.0260</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0.5903±0.0644</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0.5208±0.0170</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>0.5208±0.0170</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>0.5208±0.0170</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>0.5625±0.0510</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>0.6111±0.0644</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>0.5625±0.0741</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0.5139±0.0196</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>0.5833±0.0510</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>0.5486±0.0260</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0.5486±0.0428</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
           <t>0.5625±0.0000</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0.5417±0.0000</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>0.6458±0.0000</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>0.5833±0.0000</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>0.5833±0.0000</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0.5833±0.0000</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0.5833±0.0000</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>0.5417±0.0000</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0.6042±0.0000</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>0.5625±0.0000</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>0.5833±0.0000</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0.5417±0.0000</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>0.5625±0.0000</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0.6250±0.0000</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0.5208±0.0000</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>0.5208±0.0000</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>0.5208±0.0000</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>0.5833±0.0000</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>0.6458±0.0000</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>0.5208±0.0000</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>0.5625±0.0000</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>0.6458±0.0000</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>0.5208±0.0000</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0.5208±0.0000</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>0.5417±0.0000</t>
+          <t>0.5278±0.0428</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>0.6875±0.0000</t>
+          <t>0.6667±0.0340</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.5556±0.0428</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.5556±0.0428</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.5556±0.0428</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6042±0.0680</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>0.6042±0.0000</t>
+          <t>0.6250±0.0295</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>0.7292±0.0000</t>
+          <t>0.5486±0.0520</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.5764±0.0937</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>0.6458±0.0000</t>
+          <t>0.5347±0.0354</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>0.4792±0.0000</t>
+          <t>0.5069±0.0196</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.5000±0.0340</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.5278±0.0260</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>0.6458±0.0000</t>
+          <t>0.5833±0.0780</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>0.5625±0.0000</t>
+          <t>0.5764±0.0520</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>0.5625±0.0000</t>
+          <t>0.5208±0.0170</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>0.5625±0.0000</t>
+          <t>0.5208±0.0170</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>0.5625±0.0000</t>
+          <t>0.5208±0.0170</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.6042±0.0000</t>
+          <t>0.5556±0.0354</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6736±0.0260</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.5000±0.0170</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.6250±0.0900</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>0.5833±0.0000</t>
+          <t>0.5208±0.0295</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.4792±0.0170</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0.5208±0.0000</t>
+          <t>0.5556±0.0520</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.5208±0.0170</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0.5417±0.0000</t>
+          <t>0.5069±0.0260</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>0.5833±0.0000</t>
+          <t>0.5278±0.0260</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>0.5417±0.0000</t>
+          <t>0.5208±0.0170</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>0.5417±0.0000</t>
+          <t>0.5208±0.0170</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>0.5417±0.0000</t>
+          <t>0.5208±0.0170</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>0.6250±0.0000</t>
+          <t>0.5486±0.0260</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>0.5417±0.0000</t>
+          <t>0.6250±0.0741</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>0.5625±0.0000</t>
+          <t>0.5278±0.0393</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.5417±0.0589</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>0.5833±0.0000</t>
+          <t>0.5278±0.0260</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>0.5208±0.0000</t>
+          <t>0.5486±0.0354</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>0.5833±0.0000</t>
+          <t>0.5903±0.0354</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>0.4792±0.0000</t>
+          <t>0.5139±0.0196</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.5278±0.0687</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>0.6250±0.0000</t>
+          <t>0.5417±0.0170</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.5069±0.0260</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.5069±0.0260</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.5069±0.0260</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.5556±0.0098</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>0.5417±0.0000</t>
+          <t>0.6042±0.0450</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.5764±0.0767</t>
         </is>
       </c>
     </row>
@@ -1355,457 +1355,457 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.0690±0.0000</t>
+          <t>0.6534±0.0188</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.5965±0.0000</t>
+          <t>0.6830±0.0121</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.6761±0.0000</t>
+          <t>0.6799±0.0120</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6184±0.0410</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6635±0.0045</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.6571±0.0000</t>
+          <t>0.6413±0.0294</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.7619±0.0000</t>
+          <t>0.6809±0.0140</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6570±0.0080</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6570±0.0080</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6570±0.0080</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.6786±0.0000</t>
+          <t>0.6779±0.0094</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.6207±0.0000</t>
+          <t>0.6798±0.0263</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6836±0.0130</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.0000±0.0000</t>
+          <t>0.2222±0.3143</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6825±0.0254</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6650±0.0166</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6858±0.0367</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0.6571±0.0000</t>
+          <t>0.6703±0.0254</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.7018±0.0000</t>
+          <t>0.6865±0.0369</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>0.6875±0.0000</t>
+          <t>0.6795±0.0121</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.6774±0.0000</t>
+          <t>0.6782±0.0575</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.6774±0.0000</t>
+          <t>0.6782±0.0575</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.6774±0.0000</t>
+          <t>0.6782±0.0575</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>0.6765±0.0000</t>
+          <t>0.6666±0.0647</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6439±0.0639</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.6866±0.0000</t>
+          <t>0.6907±0.0385</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6384±0.0282</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>0.6296±0.0000</t>
+          <t>0.6803±0.0341</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6535±0.0256</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6364±0.0281</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.6765±0.0000</t>
+          <t>0.6730±0.0090</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.6957±0.0000</t>
+          <t>0.6699±0.0046</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.7273±0.0000</t>
+          <t>0.7080±0.0293</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.6761±0.0000</t>
+          <t>0.6731±0.0045</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0.6761±0.0000</t>
+          <t>0.6731±0.0045</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.6761±0.0000</t>
+          <t>0.6731±0.0045</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>0.6970±0.0000</t>
+          <t>0.6907±0.0215</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>0.7213±0.0000</t>
+          <t>0.6924±0.0492</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>0.6761±0.0000</t>
+          <t>0.6849±0.0412</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>0.6316±0.0000</t>
+          <t>0.5944±0.1021</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>0.7213±0.0000</t>
+          <t>0.6799±0.0416</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.6349±0.0000</t>
+          <t>0.6545±0.0355</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.5965±0.0000</t>
+          <t>0.6639±0.0128</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.6250±0.0000</t>
+          <t>0.6664±0.0087</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.6562±0.0000</t>
+          <t>0.6257±0.0367</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>0.7541±0.0000</t>
+          <t>0.7335±0.0247</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>0.7241±0.0000</t>
+          <t>0.6420±0.0471</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>0.7241±0.0000</t>
+          <t>0.6420±0.0471</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>0.7241±0.0000</t>
+          <t>0.6420±0.0471</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>0.7333±0.0000</t>
+          <t>0.7028±0.0418</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6991±0.0124</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>0.7797±0.0000</t>
+          <t>0.6225±0.0562</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>0.5789±0.0000</t>
+          <t>0.6550±0.0165</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>0.7018±0.0000</t>
+          <t>0.6729±0.0248</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>0.6032±0.0000</t>
+          <t>0.6410±0.0368</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6463±0.0325</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6732±0.0046</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>0.7385±0.0000</t>
+          <t>0.7018±0.0427</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>0.6957±0.0000</t>
+          <t>0.6875±0.0083</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>0.6957±0.0000</t>
+          <t>0.6626±0.0129</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>0.6957±0.0000</t>
+          <t>0.6626±0.0129</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>0.6957±0.0000</t>
+          <t>0.6626±0.0129</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0.6885±0.0000</t>
+          <t>0.6792±0.0292</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.7241±0.0000</t>
+          <t>0.7341±0.0232</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6604±0.0089</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6296±0.0524</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>0.6429±0.0000</t>
+          <t>0.6733±0.0094</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6375±0.0161</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>0.6761±0.0000</t>
+          <t>0.6901±0.0266</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6468±0.0281</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>0.6857±0.0000</t>
+          <t>0.6668±0.0154</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>0.7059±0.0000</t>
+          <t>0.6657±0.0248</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>0.6857±0.0000</t>
+          <t>0.6663±0.0081</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
         <is>
-          <t>0.6857±0.0000</t>
+          <t>0.6663±0.0081</t>
         </is>
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>0.6857±0.0000</t>
+          <t>0.6663±0.0081</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>0.7097±0.0000</t>
+          <t>0.6755±0.0299</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>0.6857±0.0000</t>
+          <t>0.7151±0.0282</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
         <is>
-          <t>0.6957±0.0000</t>
+          <t>0.6797±0.0185</t>
         </is>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>0.7143±0.0000</t>
+          <t>0.6111±0.0786</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>0.6154±0.0000</t>
+          <t>0.6657±0.0248</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>0.6761±0.0000</t>
+          <t>0.6351±0.0296</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>0.6774±0.0000</t>
+          <t>0.6811±0.0269</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>0.6479±0.0000</t>
+          <t>0.6698±0.0119</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6363±0.0220</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6589±0.0218</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6194±0.0246</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6194±0.0246</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6194±0.0246</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6862±0.0078</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>0.6857±0.0000</t>
+          <t>0.6808±0.0118</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6788±0.0462</t>
         </is>
       </c>
     </row>
@@ -1817,457 +1817,457 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.2135±0.0000</t>
+          <t>0.6215±0.2101</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.6528±0.0000</t>
+          <t>0.7402±0.0449</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.6875±0.0000</t>
+          <t>0.6288±0.0292</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.6892±0.0000</t>
+          <t>0.5706±0.0576</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.7865±0.0000</t>
+          <t>0.6881±0.0168</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.5955±0.0000</t>
+          <t>0.6719±0.0209</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.7240±0.0000</t>
+          <t>0.7645±0.0217</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.6458±0.0000</t>
+          <t>0.7274±0.0228</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.6458±0.0000</t>
+          <t>0.7274±0.0228</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.6458±0.0000</t>
+          <t>0.7274±0.0228</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.6562±0.0000</t>
+          <t>0.7211±0.0451</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.5503±0.0000</t>
+          <t>0.6123±0.0831</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.8229±0.0000</t>
+          <t>0.7277±0.0383</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.5017±0.0000</t>
+          <t>0.6476±0.0263</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.7361±0.0000</t>
+          <t>0.7378±0.0771</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.6589±0.0000</t>
+          <t>0.6140±0.0209</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.6369±0.0282</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0.7170±0.0000</t>
+          <t>0.7190±0.0258</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>0.6988±0.0000</t>
+          <t>0.7078±0.0430</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>0.7274±0.0000</t>
+          <t>0.7031±0.0748</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.6441±0.0000</t>
+          <t>0.7211±0.0484</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.6441±0.0000</t>
+          <t>0.7211±0.0484</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.6441±0.0000</t>
+          <t>0.7211±0.0484</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.6910±0.0000</t>
+          <t>0.7205±0.0814</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.7257±0.0000</t>
+          <t>0.6910±0.0743</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.6623±0.0000</t>
+          <t>0.7040±0.0627</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.6736±0.0000</t>
+          <t>0.6985±0.0426</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>0.6875±0.0000</t>
+          <t>0.7500±0.0738</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0.6823±0.0000</t>
+          <t>0.6172±0.0583</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>0.7656±0.0000</t>
+          <t>0.6285±0.1026</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.6788±0.0000</t>
+          <t>0.7095±0.0466</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.8559±0.0000</t>
+          <t>0.7222±0.0382</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.7500±0.0000</t>
+          <t>0.8038±0.0225</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.7656±0.0000</t>
+          <t>0.8131±0.0199</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.7656±0.0000</t>
+          <t>0.8131±0.0199</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.7656±0.0000</t>
+          <t>0.8131±0.0199</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>0.7170±0.0000</t>
+          <t>0.8362±0.0140</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>0.8264±0.0000</t>
+          <t>0.7274±0.0609</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>0.7917±0.0000</t>
+          <t>0.7402±0.0104</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>0.6597±0.0000</t>
+          <t>0.6858±0.0516</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>0.7188±0.0000</t>
+          <t>0.6939±0.0535</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.5174±0.0000</t>
+          <t>0.5605±0.0444</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.5512±0.0000</t>
+          <t>0.5909±0.0188</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.5139±0.0000</t>
+          <t>0.5966±0.0205</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.5547±0.0000</t>
+          <t>0.6126±0.0287</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>0.6979±0.0000</t>
+          <t>0.7564±0.0145</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.6727±0.0000</t>
+          <t>0.6302±0.0474</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>0.6727±0.0000</t>
+          <t>0.6302±0.0474</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>0.6727±0.0000</t>
+          <t>0.6302±0.0474</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>0.7014±0.0000</t>
+          <t>0.6693±0.1093</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.6736±0.0000</t>
+          <t>0.7315±0.0520</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>0.7292±0.0000</t>
+          <t>0.6403±0.0674</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.6545±0.0000</t>
+          <t>0.6400±0.0378</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>0.7153±0.0000</t>
+          <t>0.7378±0.0725</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.5773±0.0000</t>
+          <t>0.6247±0.0609</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.6910±0.0000</t>
+          <t>0.6742±0.0458</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>0.7630±0.0000</t>
+          <t>0.7613±0.0429</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>0.8420±0.0000</t>
+          <t>0.6580±0.1187</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>0.7934±0.0000</t>
+          <t>0.7610±0.0582</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>0.7969±0.0000</t>
+          <t>0.7535±0.0841</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>0.7969±0.0000</t>
+          <t>0.7535±0.0841</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>0.7969±0.0000</t>
+          <t>0.7535±0.0841</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.7135±0.0000</t>
+          <t>0.7778±0.0705</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.8108±0.0000</t>
+          <t>0.7558±0.0206</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>0.8003±0.0000</t>
+          <t>0.7303±0.0397</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>0.7535±0.0000</t>
+          <t>0.7182±0.0190</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>0.6441±0.0000</t>
+          <t>0.7089±0.0413</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>0.6259±0.0000</t>
+          <t>0.6441±0.0552</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.7170±0.0000</t>
+          <t>0.6780±0.0351</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.7578±0.0000</t>
+          <t>0.6791±0.0964</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.7535±0.0000</t>
+          <t>0.7049±0.0130</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>0.7240±0.0000</t>
+          <t>0.7951±0.0747</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>0.8108±0.0000</t>
+          <t>0.7280±0.0462</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>0.8108±0.0000</t>
+          <t>0.7280±0.0462</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>0.8108±0.0000</t>
+          <t>0.7280±0.0462</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>0.7569±0.0000</t>
+          <t>0.8044±0.0938</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>0.8507±0.0000</t>
+          <t>0.7830±0.0358</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>0.8455±0.0000</t>
+          <t>0.7321±0.0797</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>0.7465±0.0000</t>
+          <t>0.6806±0.0504</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>0.6337±0.0000</t>
+          <t>0.6997±0.0693</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6128±0.0727</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>0.7083±0.0000</t>
+          <t>0.6299±0.0667</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0.5712±0.0000</t>
+          <t>0.6808±0.0686</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>0.5955±0.0000</t>
+          <t>0.5978±0.0701</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>0.6632±0.0000</t>
+          <t>0.6626±0.0625</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>0.6753±0.0000</t>
+          <t>0.5885±0.0283</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>0.6753±0.0000</t>
+          <t>0.5885±0.0283</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>0.6753±0.0000</t>
+          <t>0.5885±0.0283</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>0.7708±0.0000</t>
+          <t>0.7760±0.0263</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>0.7899±0.0000</t>
+          <t>0.6551±0.0480</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>0.7118±0.0000</t>
+          <t>0.6866±0.0858</t>
         </is>
       </c>
     </row>
@@ -2279,457 +2279,457 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.3704±0.0000</t>
+          <t>0.6976±0.1860</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.6276±0.0000</t>
+          <t>0.7622±0.0548</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.6190±0.0000</t>
+          <t>0.5961±0.0289</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.6230±0.0000</t>
+          <t>0.5983±0.0689</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.8327±0.0000</t>
+          <t>0.7323±0.0283</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.6409±0.0000</t>
+          <t>0.6650±0.0557</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.6877±0.0000</t>
+          <t>0.7741±0.0291</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.6540±0.0000</t>
+          <t>0.7840±0.0290</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.6540±0.0000</t>
+          <t>0.7840±0.0290</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.6540±0.0000</t>
+          <t>0.7840±0.0290</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.6419±0.0000</t>
+          <t>0.7329±0.0528</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.6053±0.0000</t>
+          <t>0.6414±0.0794</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.8339±0.0000</t>
+          <t>0.7572±0.0786</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.4946±0.0000</t>
+          <t>0.7073±0.0410</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.7674±0.0000</t>
+          <t>0.7920±0.0574</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0.6159±0.0000</t>
+          <t>0.5733±0.0180</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.6297±0.0588</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.7072±0.0000</t>
+          <t>0.6959±0.0335</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.6775±0.0000</t>
+          <t>0.6772±0.0148</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.7234±0.0000</t>
+          <t>0.7656±0.0651</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.6365±0.0000</t>
+          <t>0.7377±0.0307</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.6365±0.0000</t>
+          <t>0.7377±0.0307</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.6365±0.0000</t>
+          <t>0.7377±0.0307</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.7093±0.0000</t>
+          <t>0.7610±0.0533</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.7559±0.0000</t>
+          <t>0.7604±0.0393</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.6168±0.0000</t>
+          <t>0.6710±0.0309</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.6687±0.0000</t>
+          <t>0.7404±0.0622</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>0.6752±0.0000</t>
+          <t>0.7991±0.0565</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0.6175±0.0000</t>
+          <t>0.6217±0.0575</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>0.7047±0.0000</t>
+          <t>0.6318±0.0942</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.7305±0.0000</t>
+          <t>0.6938±0.0545</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.8878±0.0000</t>
+          <t>0.7469±0.0529</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.7319±0.0000</t>
+          <t>0.8057±0.0228</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.8233±0.0000</t>
+          <t>0.8443±0.0450</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.8233±0.0000</t>
+          <t>0.8443±0.0450</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.8233±0.0000</t>
+          <t>0.8443±0.0450</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>0.6885±0.0000</t>
+          <t>0.8671±0.0156</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>0.8632±0.0000</t>
+          <t>0.7640±0.0515</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.7926±0.0000</t>
+          <t>0.7421±0.0455</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>0.6385±0.0000</t>
+          <t>0.6996±0.0713</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>0.7190±0.0000</t>
+          <t>0.7366±0.0405</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.5107±0.0000</t>
+          <t>0.5365±0.0264</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.5278±0.0000</t>
+          <t>0.5624±0.0150</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.5107±0.0000</t>
+          <t>0.5679±0.0166</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.5337±0.0000</t>
+          <t>0.5925±0.0262</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.6252±0.0000</t>
+          <t>0.7763±0.0262</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.6076±0.0000</t>
+          <t>0.6182±0.0348</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0.6076±0.0000</t>
+          <t>0.6182±0.0348</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>0.6076±0.0000</t>
+          <t>0.6182±0.0348</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>0.6323±0.0000</t>
+          <t>0.6318±0.0920</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.6676±0.0000</t>
+          <t>0.7341±0.0679</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>0.6506±0.0000</t>
+          <t>0.6586±0.0416</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.6115±0.0000</t>
+          <t>0.7127±0.0429</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>0.6945±0.0000</t>
+          <t>0.7654±0.0740</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.5712±0.0000</t>
+          <t>0.6511±0.0747</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.6225±0.0000</t>
+          <t>0.6931±0.0603</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>0.7984±0.0000</t>
+          <t>0.7710±0.0540</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>0.8677±0.0000</t>
+          <t>0.6763±0.1360</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>0.7988±0.0000</t>
+          <t>0.7774±0.0502</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>0.8393±0.0000</t>
+          <t>0.7489±0.0760</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>0.8393±0.0000</t>
+          <t>0.7489±0.0760</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>0.8393±0.0000</t>
+          <t>0.7489±0.0760</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.7259±0.0000</t>
+          <t>0.7771±0.0868</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.8546±0.0000</t>
+          <t>0.7844±0.0177</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>0.8502±0.0000</t>
+          <t>0.7392±0.0400</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>0.7780±0.0000</t>
+          <t>0.7823±0.0164</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>0.6433±0.0000</t>
+          <t>0.7413±0.0380</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>0.5738±0.0000</t>
+          <t>0.6490±0.0745</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.6977±0.0000</t>
+          <t>0.6956±0.0390</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.7979±0.0000</t>
+          <t>0.6881±0.1235</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.8047±0.0000</t>
+          <t>0.7580±0.0232</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>0.7348±0.0000</t>
+          <t>0.8242±0.0586</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>0.8447±0.0000</t>
+          <t>0.7603±0.0359</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>0.8447±0.0000</t>
+          <t>0.7603±0.0359</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>0.8447±0.0000</t>
+          <t>0.7603±0.0359</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>0.7373±0.0000</t>
+          <t>0.8168±0.0871</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>0.8594±0.0000</t>
+          <t>0.7966±0.0354</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>0.8330±0.0000</t>
+          <t>0.7674±0.0503</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>0.7795±0.0000</t>
+          <t>0.7294±0.0678</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>0.6344±0.0000</t>
+          <t>0.7232±0.0058</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>0.6063±0.0000</t>
+          <t>0.5950±0.0517</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>0.7074±0.0000</t>
+          <t>0.6388±0.0687</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>0.5960±0.0000</t>
+          <t>0.6759±0.0890</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>0.5774±0.0000</t>
+          <t>0.6101±0.0755</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>0.6294±0.0000</t>
+          <t>0.6880±0.0618</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>0.7462±0.0000</t>
+          <t>0.5784±0.0173</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>0.7462±0.0000</t>
+          <t>0.5784±0.0173</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>0.7462±0.0000</t>
+          <t>0.5784±0.0173</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>0.8285±0.0000</t>
+          <t>0.7989±0.0455</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>0.7933±0.0000</t>
+          <t>0.6713±0.0629</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>0.7810±0.0000</t>
+          <t>0.6769±0.0815</t>
         </is>
       </c>
     </row>
